--- a/multi/gpt_domain.xlsx
+++ b/multi/gpt_domain.xlsx
@@ -459,10 +459,10 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="B13" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
